--- a/db/seed/seed_NodeHierarchy_table.xlsx
+++ b/db/seed/seed_NodeHierarchy_table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skeye\BOOK2\MAKEDOC\db\seed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334C4CA3-7F5D-4FAE-9B3C-850F32156DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A3AC49-AE9D-45E8-A425-3538036B5B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="123">
   <si>
     <t>ParentNodeID</t>
   </si>
@@ -169,9 +169,6 @@
   </si>
   <si>
     <t>NL-0071</t>
-  </si>
-  <si>
-    <t>NL-0074</t>
   </si>
   <si>
     <t>NL-0075</t>
@@ -724,7 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:D110"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.33203125" customWidth="1"/>
@@ -780,7 +777,7 @@
         <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -791,7 +788,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>22</v>
@@ -862,7 +859,7 @@
         <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -873,7 +870,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
@@ -943,7 +940,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>6</v>
@@ -954,7 +951,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>15</v>
@@ -1067,7 +1064,7 @@
         <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>118</v>
       </c>
       <c r="C25" t="s">
         <v>7</v>
@@ -1078,10 +1075,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" t="s">
         <v>34</v>
-      </c>
-      <c r="B26" t="s">
-        <v>35</v>
       </c>
       <c r="C26" t="s">
         <v>7</v>
@@ -1092,10 +1089,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" t="s">
         <v>35</v>
-      </c>
-      <c r="B27" t="s">
-        <v>36</v>
       </c>
       <c r="C27" t="s">
         <v>7</v>
@@ -1106,10 +1103,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" t="s">
         <v>36</v>
-      </c>
-      <c r="B28" t="s">
-        <v>37</v>
       </c>
       <c r="C28" t="s">
         <v>7</v>
@@ -1120,10 +1117,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" t="s">
         <v>37</v>
-      </c>
-      <c r="B29" t="s">
-        <v>38</v>
       </c>
       <c r="C29" t="s">
         <v>7</v>
@@ -1134,10 +1131,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" t="s">
         <v>38</v>
-      </c>
-      <c r="B30" t="s">
-        <v>39</v>
       </c>
       <c r="C30" t="s">
         <v>7</v>
@@ -1148,10 +1145,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" t="s">
         <v>39</v>
-      </c>
-      <c r="B31" t="s">
-        <v>40</v>
       </c>
       <c r="C31" t="s">
         <v>7</v>
@@ -1162,10 +1159,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" t="s">
         <v>40</v>
-      </c>
-      <c r="B32" t="s">
-        <v>41</v>
       </c>
       <c r="C32" t="s">
         <v>7</v>
@@ -1176,10 +1173,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" t="s">
         <v>41</v>
-      </c>
-      <c r="B33" t="s">
-        <v>42</v>
       </c>
       <c r="C33" t="s">
         <v>7</v>
@@ -1190,10 +1187,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" t="s">
         <v>42</v>
-      </c>
-      <c r="B34" t="s">
-        <v>43</v>
       </c>
       <c r="C34" t="s">
         <v>7</v>
@@ -1204,6 +1201,9 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" t="s">
         <v>43</v>
       </c>
       <c r="C35" t="s">
@@ -1214,1022 +1214,1033 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="1">
-        <v>1</v>
+      <c r="A36" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36">
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>48</v>
+        <v>118</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D39" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>48</v>
+        <v>118</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D41" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="C42" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D42" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>51</v>
-      </c>
-      <c r="B43" t="s">
-        <v>52</v>
-      </c>
-      <c r="C43" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43">
-        <v>1</v>
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="1">
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C44" t="s">
         <v>9</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C45" t="s">
         <v>9</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C46" t="s">
         <v>9</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C47" t="s">
         <v>9</v>
       </c>
       <c r="D47">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C48" t="s">
         <v>9</v>
       </c>
       <c r="D48">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C49" t="s">
         <v>9</v>
       </c>
       <c r="D49">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C50" t="s">
         <v>9</v>
       </c>
       <c r="D50">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>59</v>
+        <v>57</v>
+      </c>
+      <c r="B51" t="s">
+        <v>58</v>
       </c>
       <c r="C51" t="s">
         <v>9</v>
       </c>
       <c r="D51">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52">
         <v>10</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D52" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D53" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D54" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D55" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D56" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D57" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D58" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D59" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D60" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D61" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D62" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B63" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="C63" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D63" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" s="1">
         <v>12</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>71</v>
-      </c>
-      <c r="B64" t="s">
-        <v>72</v>
-      </c>
-      <c r="C64" t="s">
-        <v>11</v>
-      </c>
-      <c r="D64">
-        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C65" t="s">
         <v>11</v>
       </c>
       <c r="D65">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C66" t="s">
         <v>11</v>
       </c>
       <c r="D66">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
       </c>
       <c r="D67">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C68" t="s">
         <v>11</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="B69" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
       </c>
       <c r="D69">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
       </c>
       <c r="D70">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
       </c>
       <c r="D71">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C72" t="s">
         <v>11</v>
       </c>
       <c r="D72">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>80</v>
+        <v>78</v>
+      </c>
+      <c r="B73" t="s">
+        <v>79</v>
       </c>
       <c r="C73" t="s">
         <v>11</v>
       </c>
       <c r="D73">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>79</v>
+      </c>
+      <c r="C74" t="s">
+        <v>11</v>
+      </c>
+      <c r="D74">
         <v>10</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D74" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D75" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D76" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D77" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D78" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D79" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D80" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D81" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D82" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D83" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D84" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D85" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D86" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D87" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B88" s="1"/>
+        <v>93</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="C88" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D88" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>98</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="B89" s="1"/>
       <c r="C89" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D89">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="D89" s="1">
+        <v>15</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D90">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D91">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D92">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D93">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D94">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D95">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D96">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B97" s="1"/>
+        <v>103</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="C97" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D97">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>107</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="B98" s="1"/>
       <c r="C98" s="1" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D99">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D100">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D101">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D102">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D103">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D104">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B105" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="D105">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="D106">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D107">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D108">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B109" s="1"/>
+        <v>116</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>117</v>
+      </c>
       <c r="C109" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D109">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B110" s="1"/>
+      <c r="C110" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D110">
         <v>12</v>
       </c>
     </row>
